--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487798_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487798_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4684</v>
+        <v>7.8794</v>
       </c>
       <c r="E2" t="n">
         <v>6.2445</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2239</v>
+        <v>1.635</v>
       </c>
       <c r="G2" t="n">
         <v>8.213100000000001</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3503</v>
+        <v>0.0607</v>
       </c>
       <c r="T2" t="n">
         <v>0.0619</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4123</v>
+        <v>-0.0012</v>
       </c>
       <c r="V2" t="n">
         <v>0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4571</v>
+        <v>6.5572</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5089</v>
+        <v>5.4018</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9481</v>
+        <v>1.1554</v>
       </c>
       <c r="G3" t="n">
         <v>6.3375</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8326</v>
+        <v>-0.0673</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1757</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9011</v>
+        <v>0.1084</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7536</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7297</v>
+        <v>5.6328</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2818</v>
+        <v>2.0675</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4479</v>
+        <v>3.5653</v>
       </c>
       <c r="G4" t="n">
         <v>5.0542</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9669</v>
+        <v>0.87</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3706</v>
+        <v>0.4881</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7076</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1948</v>
+        <v>4.8304</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7731</v>
+        <v>1.8803</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4217</v>
+        <v>2.9502</v>
       </c>
       <c r="G5" t="n">
         <v>3.8125</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.325</v>
+        <v>-0.6894</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2486</v>
+        <v>-0.1414</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0764</v>
+        <v>-0.548</v>
       </c>
       <c r="V5" t="n">
         <v>3.5804</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5027</v>
+        <v>3.2296</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6863</v>
+        <v>0.472</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8164</v>
+        <v>2.7576</v>
       </c>
       <c r="G6" t="n">
         <v>3.4116</v>
@@ -922,13 +922,13 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0047</v>
+        <v>0.7317</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3882</v>
+        <v>0.1738</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6166</v>
+        <v>0.5579</v>
       </c>
       <c r="V6" t="n">
         <v>1.1675</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3944</v>
+        <v>2.4223</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4309</v>
+        <v>-0.1095</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8253</v>
+        <v>2.5317</v>
       </c>
       <c r="G7" t="n">
         <v>4.5178</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3576</v>
+        <v>0.3855</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1833</v>
+        <v>0.1381</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5409</v>
+        <v>0.2473</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3998</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2876</v>
+        <v>1.9749</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6438</v>
+        <v>-0.751</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9314</v>
+        <v>2.7259</v>
       </c>
       <c r="G8" t="n">
         <v>1.8651</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9878</v>
+        <v>0.6751</v>
       </c>
       <c r="T8" t="n">
-        <v>0.531</v>
+        <v>0.4239</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4568</v>
+        <v>0.2513</v>
       </c>
       <c r="V8" t="n">
         <v>0.8915999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4461</v>
+        <v>1.9247</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8832</v>
+        <v>1.0975</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.8272</v>
       </c>
       <c r="G9" t="n">
         <v>2.7392</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2931</v>
+        <v>-0.8145</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5754</v>
+        <v>-0.3111</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7368</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4948</v>
+        <v>-0.3117</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.242</v>
+        <v>-0.2222</v>
       </c>
       <c r="G10" t="n">
-        <v>0.637</v>
+        <v>1.4734</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1234</v>
+        <v>2.5609</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5135</v>
+        <v>-1.0875</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7759</v>
+        <v>-0.0164</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6584</v>
+        <v>2.1447</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1176</v>
+        <v>-2.1611</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.139</v>
+        <v>1.4898</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5349</v>
+        <v>0.4162</v>
       </c>
       <c r="O10" t="n">
-        <v>0.396</v>
+        <v>1.0736</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2487</v>
+        <v>1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4587</v>
+        <v>-0.9208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0033</v>
+        <v>-0.2952</v>
       </c>
       <c r="U10" t="n">
-        <v>0.462</v>
+        <v>-0.6256</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5838</v>
+        <v>-2.3351</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9071</v>
+        <v>-0.7706</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1006</v>
+        <v>0.2078</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0077</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3621</v>
@@ -1312,13 +1312,13 @@
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3314</v>
+        <v>-0.1949</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2662</v>
+        <v>-0.2368</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6298</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2766</v>
+        <v>-1.5868</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.526</v>
+        <v>-0.8163</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7506</v>
+        <v>-0.7705</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4734</v>
+        <v>0.637</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5609</v>
+        <v>0.1234</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0875</v>
+        <v>0.5135</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0164</v>
+        <v>0.7759</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1447</v>
+        <v>0.6584</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1611</v>
+        <v>0.1176</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4898</v>
+        <v>-0.139</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4162</v>
+        <v>-0.5349</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0736</v>
+        <v>0.396</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2487</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6636</v>
+        <v>-0.3913</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3248</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1541</v>
+        <v>-0.0665</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3351</v>
+        <v>-0.5838</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.5603</v>
+        <v>31.5601</v>
       </c>
       <c r="E13" t="n">
         <v>15.3829</v>
       </c>
       <c r="F13" t="n">
-        <v>16.1774</v>
+        <v>16.1773</v>
       </c>
       <c r="G13" t="n">
         <v>37.6993</v>
@@ -1468,22 +1468,22 @@
         <v>13.5276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3551</v>
+        <v>-0.3552</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2188</v>
+        <v>-0.2188999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1363999999999996</v>
+        <v>-0.1362000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4597999999999995</v>
+        <v>0.4597999999999997</v>
       </c>
       <c r="W13" t="n">
         <v>6.509800000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.050000000000001</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8596</v>
+        <v>1.9477</v>
       </c>
       <c r="E14" t="n">
         <v>1.4559</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4037</v>
+        <v>0.4918</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0585</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5689</v>
+        <v>-0.4809</v>
       </c>
       <c r="T14" t="n">
         <v>-0.199</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3699</v>
+        <v>-0.2818</v>
       </c>
       <c r="V14" t="n">
         <v>1.8221</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1113</v>
+        <v>0.3154</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0433</v>
+        <v>2.3648</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9319</v>
+        <v>-2.0494</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8166</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7542</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0033</v>
+        <v>0.3182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7575</v>
+        <v>0.64</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8668</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7074</v>
+        <v>-0.4828</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0787</v>
+        <v>-0.9715</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3713</v>
+        <v>0.4887</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1052</v>
@@ -1702,13 +1702,13 @@
         <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8103</v>
+        <v>-0.5857</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.46</v>
+        <v>-0.3528</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3503</v>
+        <v>-0.2329</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4894</v>
+        <v>-2.0699</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5909</v>
+        <v>-1.0027</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8985</v>
+        <v>-1.0673</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.9706</v>
+        <v>-4.0738</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0919</v>
+        <v>-1.2898</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8787</v>
+        <v>-2.784</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5251</v>
+        <v>-0.2117</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2148</v>
+        <v>1.4007</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.7399</v>
+        <v>-1.6125</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4455</v>
+        <v>-3.862</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3067</v>
+        <v>-2.6905</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1388</v>
+        <v>-1.1716</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7081</v>
+        <v>0.7468</v>
       </c>
       <c r="T17" t="n">
-        <v>1.826</v>
+        <v>0.4577</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8821</v>
+        <v>0.2891</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8137</v>
+        <v>0.4246</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5838</v>
+        <v>0.4246</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2614</v>
+        <v>-2.0955</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0675</v>
+        <v>-0.9603</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1939</v>
+        <v>-1.1352</v>
       </c>
       <c r="G18" t="n">
         <v>-1.223</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4952</v>
+        <v>-0.3293</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4236</v>
+        <v>-2.1251</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4689</v>
+        <v>-1.2546</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9547</v>
+        <v>-0.8706</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0055</v>
@@ -1936,13 +1936,13 @@
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8749</v>
+        <v>-0.5765</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4476</v>
+        <v>-0.2333</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4273</v>
+        <v>-0.3431</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7692</v>
+        <v>-2.869</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3242</v>
+        <v>2.3486</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.445</v>
+        <v>-5.2177</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.0738</v>
+        <v>-1.2135</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2898</v>
+        <v>-1.269</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.784</v>
+        <v>0.0555</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2117</v>
+        <v>3.0404</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4007</v>
+        <v>1.4215</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6125</v>
+        <v>1.6189</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.862</v>
+        <v>-4.2539</v>
       </c>
       <c r="N20" t="n">
         <v>-2.6905</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1716</v>
+        <v>-1.5634</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2487</v>
+        <v>-2.4974</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0476</v>
+        <v>0.357</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1363</v>
+        <v>0.1782</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0887</v>
+        <v>0.1788</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4246</v>
+        <v>-1.8044</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4246</v>
+        <v>-3.4318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1778</v>
+        <v>-2.8736</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2415</v>
+        <v>-1.7696</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.4193</v>
+        <v>-1.104</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2135</v>
+        <v>-3.9706</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.269</v>
+        <v>-1.0919</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0555</v>
+        <v>-2.8787</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0404</v>
+        <v>-1.5251</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4215</v>
+        <v>1.2148</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6189</v>
+        <v>-2.7399</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.2539</v>
+        <v>-2.4455</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.6905</v>
+        <v>-2.3067</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5634</v>
+        <v>-0.1388</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4974</v>
+        <v>-2.2893</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0482</v>
+        <v>1.3239</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0228</v>
+        <v>0.6766</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8044</v>
+        <v>0.8137</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6275</v>
+        <v>1.3975</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.4318</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9377</v>
+        <v>-3.2194</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1635</v>
+        <v>-2.7349</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7742</v>
+        <v>-0.4845</v>
       </c>
       <c r="G22" t="n">
         <v>-5.2962</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4522</v>
+        <v>0.2661</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5905</v>
+        <v>-0.1619</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1383</v>
+        <v>0.428</v>
       </c>
       <c r="V22" t="n">
         <v>0.3538</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6054</v>
+        <v>-5.6515</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5564</v>
+        <v>-3.628</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.049</v>
+        <v>-2.0236</v>
       </c>
       <c r="G23" t="n">
         <v>-5.4981</v>
@@ -2248,13 +2248,13 @@
         <v>2.2893</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2819</v>
+        <v>0.2358</v>
       </c>
       <c r="T23" t="n">
-        <v>1.565</v>
+        <v>0.4935</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2831</v>
+        <v>-0.2577</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3892</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.1594</v>
+        <v>-11.722</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.668</v>
+        <v>-10.0251</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4914</v>
+        <v>-1.6969</v>
       </c>
       <c r="G24" t="n">
         <v>-9.438000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>2.7055</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2833</v>
+        <v>-0.8459</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3701</v>
+        <v>-0.7272</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0868</v>
+        <v>-0.1187</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8137</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.5604</v>
+        <v>-30.8457</v>
       </c>
       <c r="E25" t="n">
         <v>-16.1774</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.3829</v>
+        <v>-14.6687</v>
       </c>
       <c r="G25" t="n">
-        <v>-37.699</v>
+        <v>-37.69900000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-21.4727</v>
@@ -2377,13 +2377,13 @@
         <v>-16.2265</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.835999999999999</v>
+        <v>-8.836</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.0187</v>
+        <v>-2.018699999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.8173</v>
+        <v>-6.817299999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-28.8631</v>
@@ -2404,13 +2404,13 @@
         <v>19.7711</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3552000000000002</v>
+        <v>1.0695</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1363000000000001</v>
+        <v>0.1364</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2188999999999999</v>
+        <v>0.9332999999999998</v>
       </c>
       <c r="V25" t="n">
         <v>-0.4599000000000002</v>
